--- a/diseases/d200/2026-2029.xlsx
+++ b/diseases/d200/2026-2029.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">

--- a/diseases/d200/2026-2029.xlsx
+++ b/diseases/d200/2026-2029.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -8923,7 +8923,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9298,7 +9298,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10048,7 +10048,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -11937,7 +11937,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12326,7 +12326,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12701,7 +12701,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13076,7 +13076,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13826,7 +13826,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14201,7 +14201,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14576,7 +14576,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15326,7 +15326,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -15701,7 +15701,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16076,7 +16076,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -16451,7 +16451,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -16826,7 +16826,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17201,7 +17201,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -17576,7 +17576,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -17951,7 +17951,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18326,7 +18326,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19076,7 +19076,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -19451,7 +19451,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -19826,7 +19826,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -20201,7 +20201,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -20576,7 +20576,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -20951,7 +20951,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21326,7 +21326,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -21701,7 +21701,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -22076,7 +22076,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -22465,7 +22465,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -22704,7 +22704,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -23093,7 +23093,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -23468,7 +23468,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -23843,7 +23843,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -24218,7 +24218,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -24593,7 +24593,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -24968,7 +24968,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -25343,7 +25343,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -25718,7 +25718,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -26093,7 +26093,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -26468,7 +26468,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -26843,7 +26843,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -27218,7 +27218,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -27968,7 +27968,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
@@ -28343,7 +28343,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -28718,7 +28718,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -29093,7 +29093,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -29468,7 +29468,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -29843,7 +29843,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30218,7 +30218,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -30593,7 +30593,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -30968,7 +30968,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -31343,7 +31343,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -31718,7 +31718,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -32093,7 +32093,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -32468,7 +32468,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -32843,7 +32843,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -33232,7 +33232,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -33471,7 +33471,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -33860,7 +33860,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -34235,7 +34235,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -34610,7 +34610,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -34985,7 +34985,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -35360,7 +35360,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -35735,7 +35735,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -36110,7 +36110,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -36485,7 +36485,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -36860,7 +36860,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -37235,7 +37235,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -37610,7 +37610,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -37985,7 +37985,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -38360,7 +38360,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -38735,7 +38735,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -39110,7 +39110,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -39485,7 +39485,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -39860,7 +39860,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -40235,7 +40235,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -40610,7 +40610,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -40985,7 +40985,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -41360,7 +41360,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -41735,7 +41735,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -42110,7 +42110,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -42485,7 +42485,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -42860,7 +42860,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -43235,7 +43235,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -43610,7 +43610,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
